--- a/AAII_Financials/Yearly/YDKG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YDKG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>YDKG</t>
   </si>
@@ -713,11 +713,11 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="3">
-        <v>300</v>
-      </c>
-      <c r="F8" s="3">
-        <v>800</v>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G8" s="3">
         <v>2700</v>
@@ -743,11 +743,11 @@
       <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="3">
-        <v>300</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1400</v>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G9" s="3">
         <v>3100</v>
@@ -773,11 +773,11 @@
       <c r="D10" s="3">
         <v>-700</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-500</v>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G10" s="3">
         <v>-400</v>
@@ -820,8 +820,8 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
+      <c r="F12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G12" s="3">
         <v>0</v>
@@ -877,11 +877,11 @@
       <c r="D14" s="3">
         <v>12400</v>
       </c>
-      <c r="E14" s="3">
-        <v>3700</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-100</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
         <v>2700</v>
@@ -949,10 +949,10 @@
         <v>44300</v>
       </c>
       <c r="E17" s="3">
-        <v>7100</v>
+        <v>1800</v>
       </c>
       <c r="F17" s="3">
-        <v>4700</v>
+        <v>500</v>
       </c>
       <c r="G17" s="3">
         <v>10000</v>
@@ -979,10 +979,10 @@
         <v>-45100</v>
       </c>
       <c r="E18" s="3">
-        <v>-6800</v>
+        <v>-1800</v>
       </c>
       <c r="F18" s="3">
-        <v>-3900</v>
+        <v>-500</v>
       </c>
       <c r="G18" s="3">
         <v>-7400</v>
@@ -1023,10 +1023,10 @@
         <v>21500</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F20" s="3">
-        <v>-4200</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>-4900</v>
@@ -1053,10 +1053,10 @@
         <v>-57300</v>
       </c>
       <c r="E21" s="3">
-        <v>-6700</v>
+        <v>-2300</v>
       </c>
       <c r="F21" s="3">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="G21" s="3">
         <v>-1700</v>
@@ -1079,14 +1079,14 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G22" s="3">
         <v>800</v>
@@ -1113,10 +1113,10 @@
         <v>-78900</v>
       </c>
       <c r="E23" s="3">
-        <v>-10600</v>
+        <v>-2300</v>
       </c>
       <c r="F23" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="G23" s="3">
         <v>-6000</v>
@@ -1145,8 +1145,8 @@
       <c r="E24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1203,10 +1203,10 @@
         <v>-78900</v>
       </c>
       <c r="E26" s="3">
-        <v>-10600</v>
+        <v>-2300</v>
       </c>
       <c r="F26" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="G26" s="3">
         <v>-6000</v>
@@ -1293,10 +1293,10 @@
         <v>50900</v>
       </c>
       <c r="E29" s="3">
-        <v>-3100</v>
+        <v>-11300</v>
       </c>
       <c r="F29" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="G29" s="3">
         <v>-6300</v>
@@ -1383,10 +1383,10 @@
         <v>-21500</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="F32" s="3">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>4900</v>
@@ -1566,7 +1566,7 @@
         <v>1000</v>
       </c>
       <c r="E41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3">
         <v>200</v>
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>300</v>
@@ -1622,11 +1622,11 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
+      <c r="D43" s="3">
+        <v>1100</v>
       </c>
       <c r="E43" s="3">
-        <v>23000</v>
+        <v>4100</v>
       </c>
       <c r="F43" s="3">
         <v>22100</v>
@@ -1683,10 +1683,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>210400</v>
+        <v>206000</v>
       </c>
       <c r="E45" s="3">
-        <v>300</v>
+        <v>21800</v>
       </c>
       <c r="F45" s="3">
         <v>4900</v>
@@ -1742,8 +1742,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>9600</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
@@ -1776,7 +1776,7 @@
         <v>90900</v>
       </c>
       <c r="E48" s="3">
-        <v>34300</v>
+        <v>24300</v>
       </c>
       <c r="F48" s="3">
         <v>10200</v>
@@ -1892,11 +1892,11 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>10000</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>8</v>
@@ -2013,8 +2013,8 @@
       <c r="D57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
-        <v>11400</v>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F57" s="3">
         <v>11600</v>
@@ -2074,7 +2074,7 @@
         <v>8</v>
       </c>
       <c r="E59" s="3">
-        <v>65400</v>
+        <v>78600</v>
       </c>
       <c r="F59" s="3">
         <v>70900</v>
@@ -2706,11 +2706,11 @@
       <c r="D83" s="3">
         <v>9200</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1000</v>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G83" s="3">
         <v>800</v>
